--- a/data/mobile.xlsx
+++ b/data/mobile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lzz/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lzz/github_teaching/emetrics26/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D31E916-DA50-8445-A0F0-755D631F020F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF386AAE-5021-9046-91E1-9EBAFF431686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="9" r:id="rId1"/>
@@ -29,9 +29,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
   </pivotCaches>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -71,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2684" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2684" uniqueCount="498">
   <si>
     <t>序号</t>
   </si>
@@ -1724,6 +1723,18 @@
   </si>
   <si>
     <t>value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cost</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>brand_prefer</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>demand_type</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3741,7 +3752,71 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D13373F3-AE60-0F48-8A66-7F60ECB0948F}" name="数据透视表2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6AE9D71F-AB71-154E-B457-F4D4B702161D}" name="数据透视表1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+  <location ref="A3:B10" firstHeaderRow="2" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" compact="0" outline="0" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="计数项:6、您认为自己最接近哪类用户？ " fld="7" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D13373F3-AE60-0F48-8A66-7F60ECB0948F}" name="数据透视表2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A20:B27" firstHeaderRow="2" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -3800,70 +3875,6 @@
   </colItems>
   <dataFields count="1">
     <dataField name="计数项:7、在购买笔记本电脑时，您最看重或倾向于选择哪类品牌：" fld="8" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6AE9D71F-AB71-154E-B457-F4D4B702161D}" name="数据透视表1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
-  <location ref="A3:B10" firstHeaderRow="2" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" compact="0" outline="0" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="计数项:6、您认为自己最接近哪类用户？ " fld="7" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -4189,7 +4200,7 @@
         <v>433</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>429</v>
+        <v>495</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>431</v>
@@ -4201,10 +4212,10 @@
         <v>456</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>440</v>
+        <v>497</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>444</v>
+        <v>496</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.15">
